--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_Fig05_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_Fig05_source_data.xlsx
@@ -7864,13 +7864,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7.083333333333334</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.625</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>9.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7884,16 +7884,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>7.12962962962963</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3.012152777777778</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>14.72800925925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7901,22 +7901,22 @@
         <v>45872</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04340277777777778</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2256944444444444</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4.444444444444445</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6799768518518519</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>19.7974537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7924,22 +7924,22 @@
         <v>45873</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04050925925925926</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3645833333333334</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>10.02893518518519</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2.135416666666667</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>18.44328703703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7947,22 +7947,22 @@
         <v>45874</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1967592592592593</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04918981481481482</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1.802662037037037</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6.400462962962963</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.34837962962963</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>14.61226851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7970,22 +7970,22 @@
         <v>45875</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1678240740740741</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7696759259259259</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>7.991898148148148</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3.359375</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>26.79976851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7993,22 +7993,22 @@
         <v>45876</v>
       </c>
       <c r="B8" t="n">
-        <v>0.162037037037037</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5584490740740742</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5.873842592592593</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7783564814814815</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>23.12210648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8016,22 +8016,22 @@
         <v>45877</v>
       </c>
       <c r="B9" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1.102430555555556</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7.054398148148148</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8825231481481481</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.39641203703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8039,22 +8039,22 @@
         <v>45878</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5121527777777779</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>11.08217592592593</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4.039351851851852</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>21.88368055555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -8062,22 +8062,22 @@
         <v>45879</v>
       </c>
       <c r="B11" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6684027777777778</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>7.065972222222222</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.252893518518519</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>19.5630787037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -8085,22 +8085,22 @@
         <v>45880</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5.734953703703704</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.623263888888889</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>17.61574074074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8108,22 +8108,22 @@
         <v>45881</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06365740740740741</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>4.525462962962963</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8043981481481481</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>13.00347222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8131,22 +8131,22 @@
         <v>45882</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3645833333333333</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>15.65393518518519</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5.104166666666667</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>21.95023148148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8154,22 +8154,22 @@
         <v>45883</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04050925925925926</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002893518518518519</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5989583333333333</v>
+        <v>0.3993055555555556</v>
       </c>
       <c r="E15" t="n">
-        <v>12.50578703703704</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="F15" t="n">
-        <v>3.547453703703704</v>
+        <v>0.3472222222222222</v>
       </c>
       <c r="G15" t="n">
-        <v>17.05439814814815</v>
+        <v>0.3645833333333333</v>
       </c>
     </row>
     <row r="16">
@@ -8177,22 +8177,22 @@
         <v>45884</v>
       </c>
       <c r="B16" t="n">
-        <v>2.702546296296297</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="C16" t="n">
-        <v>2.309027777777778</v>
+        <v>8.680555555555557</v>
       </c>
       <c r="D16" t="n">
-        <v>3.165509259259259</v>
+        <v>9.097222222222221</v>
       </c>
       <c r="E16" t="n">
-        <v>11.92708333333333</v>
+        <v>8.912037037037038</v>
       </c>
       <c r="F16" t="n">
-        <v>6.467013888888889</v>
+        <v>8.767361111111111</v>
       </c>
       <c r="G16" t="n">
-        <v>18.16840277777778</v>
+        <v>9.02199074074074</v>
       </c>
     </row>
     <row r="17">
@@ -8200,22 +8200,22 @@
         <v>45885</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1331018518518519</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6047453703703703</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>20.3587962962963</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>12.04282407407407</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>44.74247685185186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -8223,22 +8223,22 @@
         <v>45886</v>
       </c>
       <c r="B18" t="n">
-        <v>0.04050925925925926</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.002893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5208333333333333</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7025462962963</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>7.826967592592592</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>45.82465277777777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -8246,22 +8246,22 @@
         <v>45887</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6597222222222223</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6.001157407407407</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8796296296296295</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>17.47685185185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -8269,22 +8269,22 @@
         <v>45888</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1793981481481481</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7494212962962963</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>15.08680555555556</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>12.96585648148148</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>20.08101851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -8292,22 +8292,22 @@
         <v>45889</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1331018518518519</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2575231481481481</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>15.73495370370371</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>6.11400462962963</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>27.48263888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -8315,22 +8315,22 @@
         <v>45890</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.611111111111111</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>3.266782407407407</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>17.2800925925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -8338,22 +8338,22 @@
         <v>45891</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1909722222222222</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>10.59027777777778</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.722800925925926</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>17.53761574074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -8361,22 +8361,22 @@
         <v>45892</v>
       </c>
       <c r="B24" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>11.53935185185185</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3.058449074074074</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>22.97164351851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -8384,22 +8384,22 @@
         <v>45893</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>9.456018518518517</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>2.268518518518518</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>19.56018518518518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -8407,22 +8407,22 @@
         <v>45894</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1909722222222222</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>4.444444444444445</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2.511574074074074</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>17.93981481481482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -8430,22 +8430,22 @@
         <v>45895</v>
       </c>
       <c r="B27" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2604166666666666</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>4.988425925925926</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>3.695023148148148</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>15.22280092592592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -8453,22 +8453,22 @@
         <v>45896</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>7.07175925925926</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2.560763888888889</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>16.25289351851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -8476,22 +8476,22 @@
         <v>45897</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3530092592592593</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>7.887731481481481</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>5.497685185185185</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>18.48958333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -8499,22 +8499,22 @@
         <v>45898</v>
       </c>
       <c r="B30" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>7.945601851851851</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>2.32349537037037</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>17.96006944444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -8522,22 +8522,22 @@
         <v>45899</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>9.33449074074074</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1.524884259259259</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>13.93229166666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -8545,22 +8545,22 @@
         <v>45900</v>
       </c>
       <c r="B32" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1012731481481482</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>14.20717592592592</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>4.259259259259259</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>19.73668981481482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -8568,22 +8568,22 @@
         <v>45901</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0462962962962963</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2922453703703703</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>12.55208333333333</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>7.916666666666666</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>22.21354166666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -8591,22 +8591,22 @@
         <v>45902</v>
       </c>
       <c r="B34" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.041666666666666</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1.99074074074074</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>11.54224537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -8614,22 +8614,22 @@
         <v>45903</v>
       </c>
       <c r="B35" t="n">
-        <v>0.2141203703703704</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4282407407407408</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>10.43981481481481</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1.909722222222222</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>20.74942129629629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -8637,22 +8637,22 @@
         <v>45904</v>
       </c>
       <c r="B36" t="n">
-        <v>0.6539351851851851</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4195601851851851</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="D36" t="n">
-        <v>0.7494212962962964</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E36" t="n">
-        <v>14.58333333333333</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="F36" t="n">
-        <v>5.052083333333333</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>24.31423611111111</v>
+        <v>0.2083333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -8660,22 +8660,22 @@
         <v>45905</v>
       </c>
       <c r="B37" t="n">
-        <v>0.4282407407407407</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2980324074074074</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5931712962962963</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>11.38888888888889</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>4.768518518518519</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>25.36168981481481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -8683,22 +8683,22 @@
         <v>45906</v>
       </c>
       <c r="B38" t="n">
-        <v>0.2488425925925926</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0.09837962962962964</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.5034722222222222</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>11.50462962962963</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>6.244212962962963</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>29.59490740740741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -8706,22 +8706,22 @@
         <v>45907</v>
       </c>
       <c r="B39" t="n">
-        <v>0.2314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2141203703703704</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2662037037037037</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>16.64351851851852</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>9.221643518518519</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>29.16087962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -8729,22 +8729,22 @@
         <v>45908</v>
       </c>
       <c r="B40" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1.197916666666667</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>18.89467592592592</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>12.75173611111111</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>38.42303240740741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -8752,22 +8752,22 @@
         <v>45909</v>
       </c>
       <c r="B41" t="n">
-        <v>0.3587962962962963</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1012731481481481</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>2.734375</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>17.14699074074074</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>14.921875</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>24.34606481481481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -8775,22 +8775,22 @@
         <v>45910</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0925925925925926</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0.04340277777777778</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.89525462962963</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>22.12962962962963</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>17.28587962962963</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>37.88483796296296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -8804,16 +8804,16 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>1.197916666666667</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>23.42013888888889</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>18.27256944444444</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>31.63194444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -8821,22 +8821,22 @@
         <v>45912</v>
       </c>
       <c r="B44" t="n">
-        <v>3.715277777777778</v>
+        <v>25.3125</v>
       </c>
       <c r="C44" t="n">
-        <v>3.498263888888888</v>
+        <v>25.20833333333333</v>
       </c>
       <c r="D44" t="n">
-        <v>3.993055555555555</v>
+        <v>25.41666666666667</v>
       </c>
       <c r="E44" t="n">
-        <v>11.79398148148148</v>
+        <v>25.27777777777778</v>
       </c>
       <c r="F44" t="n">
-        <v>6.67824074074074</v>
+        <v>25.20833333333333</v>
       </c>
       <c r="G44" t="n">
-        <v>15.76388888888889</v>
+        <v>25.39930555555556</v>
       </c>
     </row>
     <row r="45">
@@ -8844,22 +8844,22 @@
         <v>45913</v>
       </c>
       <c r="B45" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2170138888888889</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>14.43287037037037</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>7.879050925925926</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>20.83912037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -8867,22 +8867,22 @@
         <v>45914</v>
       </c>
       <c r="B46" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1909722222222222</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>13.76157407407407</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>7.245370370370371</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>24.140625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -8890,22 +8890,22 @@
         <v>45915</v>
       </c>
       <c r="B47" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3993055555555556</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>17.57523148148148</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>10.40219907407407</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>27.76041666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -8913,22 +8913,22 @@
         <v>45916</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5815972222222223</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>19.20138888888889</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>4.192708333333333</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>30.14756944444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8936,22 +8936,22 @@
         <v>45917</v>
       </c>
       <c r="B49" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2517361111111111</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>17.11226851851852</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>14.59780092592593</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>34.74826388888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -8959,22 +8959,22 @@
         <v>45918</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1909722222222222</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>18.49537037037037</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>14.27951388888889</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>20.15046296296296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -8988,16 +8988,16 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>14.83796296296297</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>14.54861111111111</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>21.20370370370371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -9005,22 +9005,22 @@
         <v>45920</v>
       </c>
       <c r="B52" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>12.98611111111111</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>4.401041666666667</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>27.90798611111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -9028,22 +9028,22 @@
         <v>45921</v>
       </c>
       <c r="B53" t="n">
-        <v>0.005787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.05497685185185185</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>9.837962962962964</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>5.150462962962963</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>17.01678240740741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -9051,22 +9051,22 @@
         <v>45922</v>
       </c>
       <c r="B54" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>8.993055555555555</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>2.488425925925926</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>15.6712962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -9080,16 +9080,16 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>8.831018518518517</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>3.391203703703704</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>14.56597222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -9097,22 +9097,22 @@
         <v>45924</v>
       </c>
       <c r="B56" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1851851851851852</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>6.840277777777778</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>2.77199074074074</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>14.39814814814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -9126,16 +9126,16 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>5.943287037037036</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>4.039351851851851</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>11.65798611111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -9149,16 +9149,16 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>8.686342592592592</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>2.977430555555555</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>14.39525462962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -9166,22 +9166,22 @@
         <v>45927</v>
       </c>
       <c r="B59" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>18.09606481481481</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>8.203125</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>22.50289351851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -9189,22 +9189,22 @@
         <v>45928</v>
       </c>
       <c r="B60" t="n">
-        <v>0.08101851851851852</v>
+        <v>0</v>
       </c>
       <c r="C60" t="n">
-        <v>0.005787037037037038</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>12.04282407407407</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>10.97222222222222</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>31.15162037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -9212,22 +9212,22 @@
         <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.09837962962962965</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>10.98958333333333</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>3.969907407407407</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>33.2175925925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -9235,22 +9235,22 @@
         <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C62" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>11.04166666666667</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>6.660879629629629</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>29.58912037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -9258,22 +9258,22 @@
         <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0.08969907407407408</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>10.84490740740741</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>6.866319444444445</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>19.64120370370371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -9281,22 +9281,22 @@
         <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0462962962962963</v>
+        <v>0</v>
       </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0.1012731481481482</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>9.849537037037038</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>7.945601851851851</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>15.53819444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -9304,22 +9304,22 @@
         <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0.09548611111111112</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>6.493055555555556</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>3.978587962962964</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>18.07002314814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -9333,16 +9333,16 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.08680555555555557</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>10.9837962962963</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>8.501157407407408</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>12.08622685185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -9356,16 +9356,16 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.08680555555555557</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>11.86342592592592</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>10.35590277777778</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>26.64351851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -9382,13 +9382,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>18.70949074074074</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>12.34375</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>26.72453703703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -9396,22 +9396,22 @@
         <v>45937</v>
       </c>
       <c r="B69" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>14.25925925925926</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>11.93865740740741</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>18.23784722222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -9419,22 +9419,22 @@
         <v>45938</v>
       </c>
       <c r="B70" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>8.119212962962962</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>6.927083333333334</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>13.39988425925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -9442,22 +9442,22 @@
         <v>45939</v>
       </c>
       <c r="B71" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>8.645833333333334</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>6.85474537037037</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>11.96469907407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -9465,22 +9465,22 @@
         <v>45940</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1273148148148148</v>
+        <v>0</v>
       </c>
       <c r="C72" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2199074074074074</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>13.27546296296296</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>8.923611111111112</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>22.55787037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -9488,22 +9488,22 @@
         <v>45941</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0925925925925926</v>
+        <v>0</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2025462962962963</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>14.98842592592593</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>12.44502314814815</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>32.27141203703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -9517,16 +9517,16 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.1302083333333333</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>15.92013888888889</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>9.534143518518517</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>34.63252314814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -9534,22 +9534,22 @@
         <v>45943</v>
       </c>
       <c r="B75" t="n">
-        <v>0.2430555555555556</v>
+        <v>0</v>
       </c>
       <c r="C75" t="n">
-        <v>0.04918981481481481</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3327546296296297</v>
+        <v>0.02604166666666667</v>
       </c>
       <c r="E75" t="n">
-        <v>15.32407407407407</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>12.421875</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>30.7349537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -9557,22 +9557,22 @@
         <v>45944</v>
       </c>
       <c r="B76" t="n">
-        <v>0.04050925925925926</v>
+        <v>0.01736111111111111</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1765046296296297</v>
+        <v>0.0607638888888889</v>
       </c>
       <c r="E76" t="n">
-        <v>10.54976851851852</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>7.818287037037036</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>13.40277777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -9580,22 +9580,22 @@
         <v>45945</v>
       </c>
       <c r="B77" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.1736111111111111</v>
+        <v>0.06944444444444445</v>
       </c>
       <c r="E77" t="n">
-        <v>10.18518518518519</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>3.810763888888889</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>11.49016203703704</v>
+        <v>0.05208333333333334</v>
       </c>
     </row>
     <row r="78">
@@ -9603,22 +9603,22 @@
         <v>45946</v>
       </c>
       <c r="B78" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.1707175925925926</v>
+        <v>0.03472222222222222</v>
       </c>
       <c r="E78" t="n">
-        <v>8.940972222222223</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>3.967013888888889</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>15.76388888888889</v>
+        <v>0.03472222222222222</v>
       </c>
     </row>
     <row r="79">
@@ -9626,22 +9626,22 @@
         <v>45947</v>
       </c>
       <c r="B79" t="n">
-        <v>0.04050925925925926</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.002893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>6.984953703703703</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>2.392939814814815</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>22.93981481481481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -9649,22 +9649,22 @@
         <v>45948</v>
       </c>
       <c r="B80" t="n">
-        <v>0.05208333333333334</v>
+        <v>0.01736111111111111</v>
       </c>
       <c r="C80" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.06944444444444445</v>
+        <v>0.0607638888888889</v>
       </c>
       <c r="E80" t="n">
-        <v>6.684027777777777</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1.142939814814815</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>15.5931712962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -9678,16 +9678,16 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>13.18287037037037</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>6.030092592592592</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>20.5613425925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -9695,22 +9695,22 @@
         <v>45950</v>
       </c>
       <c r="B82" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.06365740740740741</v>
+        <v>0.008680555555555556</v>
       </c>
       <c r="E82" t="n">
-        <v>10.09259259259259</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4.762731481481482</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>22.28009259259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -9718,22 +9718,22 @@
         <v>45951</v>
       </c>
       <c r="B83" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4947916666666667</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>6.452546296296296</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>5.05787037037037</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>11.07638888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -9741,22 +9741,22 @@
         <v>45952</v>
       </c>
       <c r="B84" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.3298611111111111</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>4.762731481481481</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>4.111689814814815</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>6.108217592592593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -9764,22 +9764,22 @@
         <v>45953</v>
       </c>
       <c r="B85" t="n">
-        <v>0.02314814814814815</v>
+        <v>0.01157407407407408</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.06365740740740741</v>
+        <v>0.05787037037037038</v>
       </c>
       <c r="E85" t="n">
-        <v>3.912037037037037</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>2.248263888888889</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>4.560185185185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -9790,19 +9790,19 @@
         <v>0.02314814814814815</v>
       </c>
       <c r="C86" t="n">
-        <v>0.005787037037037038</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.04050925925925927</v>
+        <v>0.06365740740740741</v>
       </c>
       <c r="E86" t="n">
-        <v>5.561342592592592</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>3.836805555555556</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>7.251157407407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -9810,22 +9810,22 @@
         <v>45955</v>
       </c>
       <c r="B87" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.08391203703703705</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>3.356481481481481</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>2.69386574074074</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>7.265625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -9833,22 +9833,22 @@
         <v>45956</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0462962962962963</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>2.337962962962963</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>2.039930555555555</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>3.49537037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -9856,22 +9856,22 @@
         <v>45957</v>
       </c>
       <c r="B89" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>3.315972222222222</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>2.141203703703703</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>6.808449074074074</v>
+        <v>0.05208333333333334</v>
       </c>
     </row>
     <row r="90">
@@ -9885,16 +9885,16 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>3.414351851851852</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1.869212962962963</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>4.733796296296296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -9902,22 +9902,22 @@
         <v>45959</v>
       </c>
       <c r="B91" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.1302083333333333</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>4.357638888888889</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>3.179976851851852</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>12.75752314814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -9925,22 +9925,22 @@
         <v>45960</v>
       </c>
       <c r="B92" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="C92" t="n">
-        <v>0.02604166666666667</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.1909722222222222</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>7.314814814814815</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>2.277199074074074</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>21.62326388888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -9954,16 +9954,16 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>5.27199074074074</v>
+        <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>1.909722222222222</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>27.29745370370371</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -9977,16 +9977,16 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2690972222222222</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>6.984953703703704</v>
+        <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1.970486111111111</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>22.77199074074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -10000,16 +10000,16 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>4.363425925925926</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>2.424768518518518</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>6.753472222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -10023,16 +10023,16 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>2.847222222222222</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>2.352430555555556</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>3.28125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -10046,16 +10046,16 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>3.674768518518519</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>3.116319444444444</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>4.641203703703703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -10063,22 +10063,22 @@
         <v>45966</v>
       </c>
       <c r="B98" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4513888888888889</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
-        <v>6.44675925925926</v>
+        <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>3.804976851851852</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>27.27430555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -10092,16 +10092,16 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>6.52199074074074</v>
+        <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>5.373263888888888</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>12.67939814814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -10109,22 +10109,22 @@
         <v>45968</v>
       </c>
       <c r="B100" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
-        <v>7.025462962962964</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>3.914930555555555</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>16.66377314814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -10132,22 +10132,22 @@
         <v>45969</v>
       </c>
       <c r="B101" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.6655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>11.29050925925926</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>7.03125</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>13.14525462962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -10155,22 +10155,22 @@
         <v>45970</v>
       </c>
       <c r="B102" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.3298611111111112</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>11.5162037037037</v>
+        <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>6.296296296296297</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>17.90798611111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -10178,22 +10178,22 @@
         <v>45971</v>
       </c>
       <c r="B103" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C103" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0.546875</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>10.50925925925926</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>5.52662037037037</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>22.0630787037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -10201,22 +10201,22 @@
         <v>45972</v>
       </c>
       <c r="B104" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>1.458333333333333</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>9.230324074074074</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>5.05787037037037</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>16.26736111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -10224,22 +10224,22 @@
         <v>45973</v>
       </c>
       <c r="B105" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5989583333333333</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>17.12962962962963</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>11.12268518518518</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>24.53414351851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -10247,22 +10247,22 @@
         <v>45974</v>
       </c>
       <c r="B106" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.3877314814814814</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>15.05208333333333</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>5.842013888888888</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>23.203125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -10270,22 +10270,22 @@
         <v>45975</v>
       </c>
       <c r="B107" t="n">
-        <v>0.04050925925925926</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>0.002893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0.8159722222222223</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>14.36921296296296</v>
+        <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>7.196180555555555</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>25.92592592592592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -10293,22 +10293,22 @@
         <v>45976</v>
       </c>
       <c r="B108" t="n">
-        <v>0.1331018518518519</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
-        <v>0.03182870370370371</v>
+        <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.6944444444444444</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>4.890046296296296</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>2.647569444444445</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>20.1099537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -10316,22 +10316,22 @@
         <v>45977</v>
       </c>
       <c r="B109" t="n">
-        <v>0.1793981481481481</v>
+        <v>0</v>
       </c>
       <c r="C109" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>1.773726851851852</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>12.15856481481482</v>
+        <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>5.677083333333334</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>19.9681712962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -10339,22 +10339,22 @@
         <v>45978</v>
       </c>
       <c r="B110" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.7899305555555557</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>7.222222222222223</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>5.298032407407407</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>16.8113425925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -10362,22 +10362,22 @@
         <v>45979</v>
       </c>
       <c r="B111" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>1.09375</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>6.892361111111112</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>6.652199074074074</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>19.39814814814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -10385,22 +10385,22 @@
         <v>45980</v>
       </c>
       <c r="B112" t="n">
-        <v>1.018518518518518</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="C112" t="n">
-        <v>0.859375</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="D112" t="n">
-        <v>2.071759259259259</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="E112" t="n">
-        <v>8.153935185185185</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="F112" t="n">
-        <v>4.360532407407407</v>
+        <v>1.180555555555556</v>
       </c>
       <c r="G112" t="n">
-        <v>15.95775462962963</v>
+        <v>1.180555555555556</v>
       </c>
     </row>
     <row r="113">
@@ -10408,22 +10408,22 @@
         <v>45981</v>
       </c>
       <c r="B113" t="n">
-        <v>0.162037037037037</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1302083333333333</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D113" t="n">
-        <v>0.931712962962963</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="E113" t="n">
-        <v>20.625</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="F113" t="n">
-        <v>11.01273148148148</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="G113" t="n">
-        <v>30.77546296296296</v>
+        <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="114">
@@ -10431,22 +10431,22 @@
         <v>45982</v>
       </c>
       <c r="B114" t="n">
-        <v>0.08680555555555557</v>
+        <v>0</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.5642361111111112</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>16.23263888888889</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>8.125</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>30.40798611111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -10454,22 +10454,22 @@
         <v>45983</v>
       </c>
       <c r="B115" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1128472222222222</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>7.957175925925926</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>5.44849537037037</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>17.17592592592592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -10477,22 +10477,22 @@
         <v>45984</v>
       </c>
       <c r="B116" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2256944444444445</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>18.42592592592593</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>9.872685185185185</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>36.45833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -10506,16 +10506,16 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>33.95833333333334</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>11.33101851851852</v>
+        <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>48.5300925925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -10529,16 +10529,16 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>13.13657407407407</v>
+        <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>5.457175925925926</v>
+        <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>25.33854166666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -10546,22 +10546,22 @@
         <v>45987</v>
       </c>
       <c r="B119" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>5.572916666666666</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>3.428819444444445</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>17.09201388888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -10578,13 +10578,13 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>18.46643518518518</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>4.253472222222222</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>35.7349537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -10598,16 +10598,16 @@
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>15.97800925925926</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>4.965277777777778</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>27.69386574074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -10621,16 +10621,16 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E122" t="n">
-        <v>19.62962962962963</v>
+        <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>10.24594907407407</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>33.41435185185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -10638,22 +10638,22 @@
         <v>45991</v>
       </c>
       <c r="B123" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>28.53587962962963</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>12.3119212962963</v>
+        <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>36.81712962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -10661,22 +10661,22 @@
         <v>45992</v>
       </c>
       <c r="B124" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>22.60416666666666</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>11.11979166666667</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>34.16666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -10690,16 +10690,16 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.06076388888888889</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>23.29861111111111</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>8.796296296296298</v>
+        <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>31.02141203703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -10713,16 +10713,16 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>17.15277777777778</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>7.155671296296296</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>24.37210648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -10730,22 +10730,22 @@
         <v>45995</v>
       </c>
       <c r="B127" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>29.17824074074074</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>12.37847222222222</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>41.88078703703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -10753,22 +10753,22 @@
         <v>45996</v>
       </c>
       <c r="B128" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>31.62037037037037</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>9.57175925925926</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>58.66030092592593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -10785,13 +10785,13 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>40.13310185185185</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>14.05381944444444</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>65.49189814814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -10799,22 +10799,22 @@
         <v>45998</v>
       </c>
       <c r="B130" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>34.87847222222222</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>13.20601851851852</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>72.02835648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -10828,16 +10828,16 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>28.08449074074074</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>13.85416666666667</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>43.66898148148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -10845,22 +10845,22 @@
         <v>46000</v>
       </c>
       <c r="B132" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1128472222222222</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>32.23958333333334</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>12.26273148148148</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>39.23900462962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -10874,16 +10874,16 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>24.29976851851852</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>10.82175925925926</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>46.78819444444444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -10897,16 +10897,16 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E134" t="n">
-        <v>28.26967592592592</v>
+        <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>11.00983796296296</v>
+        <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>60.96354166666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -10920,16 +10920,16 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>32.18171296296296</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>14.97106481481481</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>48.48958333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -10946,13 +10946,13 @@
         <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>23.31597222222222</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>10.07523148148148</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>32.11226851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -10960,22 +10960,22 @@
         <v>46005</v>
       </c>
       <c r="B137" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>23.44328703703704</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>11.42071759259259</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>35.7175925925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -10989,16 +10989,16 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
-        <v>13.0150462962963</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>7.945601851851851</v>
+        <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>14.19560185185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -11006,22 +11006,22 @@
         <v>46007</v>
       </c>
       <c r="B139" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>11.23842592592593</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>4.939236111111111</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>27.81539351851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -11035,16 +11035,16 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.02604166666666667</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
-        <v>12.62152777777778</v>
+        <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>4.059606481481482</v>
+        <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>30.2806712962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -11052,22 +11052,22 @@
         <v>46009</v>
       </c>
       <c r="B141" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>11.38888888888889</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>3.587962962962963</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>27.04571759259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -11081,16 +11081,16 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
-        <v>10.90277777777778</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>3.197337962962963</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>23.53009259259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -11104,16 +11104,16 @@
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>12.17013888888889</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>5.251736111111111</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>21.90972222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -11121,22 +11121,22 @@
         <v>46012</v>
       </c>
       <c r="B144" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C144" t="n">
-        <v>0.01446759259259259</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>15.23726851851852</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>7.297453703703703</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>29.80902777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -11144,22 +11144,22 @@
         <v>46013</v>
       </c>
       <c r="B145" t="n">
-        <v>0.1446759259259259</v>
+        <v>0</v>
       </c>
       <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.4195601851851852</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>13.55324074074074</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>8.625578703703702</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>27.44791666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -11167,22 +11167,22 @@
         <v>46014</v>
       </c>
       <c r="B146" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>10.55555555555556</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>5.674189814814814</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>23.70949074074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -11190,22 +11190,22 @@
         <v>46015</v>
       </c>
       <c r="B147" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0.1012731481481482</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>13.59375</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>6.866319444444445</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>25.42534722222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -11213,22 +11213,22 @@
         <v>46016</v>
       </c>
       <c r="B148" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1302083333333334</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>20.81018518518518</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>11.64641203703704</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>32.43055555555555</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -11236,22 +11236,22 @@
         <v>46017</v>
       </c>
       <c r="B149" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>15.21990740740741</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>11.84027777777778</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>19.72800925925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -11265,16 +11265,16 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>9.994212962962962</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>6.278935185185184</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>21.19212962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -11288,16 +11288,16 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>16.01273148148148</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>10.70601851851852</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>22.92534722222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -11305,22 +11305,22 @@
         <v>46020</v>
       </c>
       <c r="B152" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.234375</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>14.76273148148148</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>5.844907407407407</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>25.58159722222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -11334,16 +11334,16 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>17.4537037037037</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>8.4375</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>21.53935185185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -11351,22 +11351,22 @@
         <v>46022</v>
       </c>
       <c r="B154" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>13.74421296296296</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>7.418981481481481</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>22.71701388888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -11374,22 +11374,22 @@
         <v>46023</v>
       </c>
       <c r="B155" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0.2633101851851852</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>16.4525462962963</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>7.994791666666666</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>21.33391203703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -11397,22 +11397,22 @@
         <v>46024</v>
       </c>
       <c r="B156" t="n">
-        <v>0.005787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1938657407407408</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>10.3125</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>6.166087962962963</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>16.36863425925926</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -11426,16 +11426,16 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>10.7349537037037</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>10.28935185185185</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>14.83506944444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -11449,16 +11449,16 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>17.00231481481482</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>11.81423611111111</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>20.81886574074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -11472,16 +11472,16 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>11.20949074074074</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>7.210648148148149</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>16.26736111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -11489,22 +11489,22 @@
         <v>46028</v>
       </c>
       <c r="B160" t="n">
-        <v>0.2141203703703704</v>
+        <v>36.18055555555556</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1822916666666667</v>
+        <v>36.18055555555556</v>
       </c>
       <c r="D160" t="n">
-        <v>0.3414351851851852</v>
+        <v>36.18055555555556</v>
       </c>
       <c r="E160" t="n">
-        <v>5.231481481481482</v>
+        <v>36.18055555555556</v>
       </c>
       <c r="F160" t="n">
-        <v>1.336805555555556</v>
+        <v>36.18055555555556</v>
       </c>
       <c r="G160" t="n">
-        <v>7.858796296296297</v>
+        <v>36.18055555555556</v>
       </c>
     </row>
     <row r="161">
@@ -11512,22 +11512,22 @@
         <v>46029</v>
       </c>
       <c r="B161" t="n">
-        <v>0.1909722222222222</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="C161" t="n">
-        <v>0.06944444444444445</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="D161" t="n">
-        <v>0.3298611111111112</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="E161" t="n">
-        <v>21.49884259259259</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="F161" t="n">
-        <v>12.37847222222222</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="G161" t="n">
-        <v>31.89525462962963</v>
+        <v>3.958333333333333</v>
       </c>
     </row>
     <row r="162">
@@ -11541,16 +11541,16 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>25.49189814814815</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>17.09490740740741</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>32.31770833333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -11567,13 +11567,13 @@
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>29.05671296296296</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>20.16782407407408</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>33.20601851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -11587,16 +11587,16 @@
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>22.45370370370371</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>19.37210648148148</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>29.75405092592592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -11610,16 +11610,16 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0.02604166666666667</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>23.41435185185185</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>10.22569444444444</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>32.09780092592592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -11627,22 +11627,22 @@
         <v>46034</v>
       </c>
       <c r="B166" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>17.04282407407407</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>6.762152777777779</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>24.54571759259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -11656,16 +11656,16 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0.06076388888888889</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>14.7337962962963</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>10.61342592592593</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>21.57986111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -11682,13 +11682,13 @@
         <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>20.79282407407408</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>18.88310185185185</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>24.27372685185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -11702,16 +11702,16 @@
         <v>0</v>
       </c>
       <c r="D169" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>14.40972222222222</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>10.43981481481481</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>19.0306712962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -11725,16 +11725,16 @@
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>18.95833333333334</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>14.88425925925926</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>23.84837962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -11742,22 +11742,22 @@
         <v>46039</v>
       </c>
       <c r="B171" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.2256944444444444</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>21.89814814814815</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>15.50347222222222</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>30.6105324074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -11765,22 +11765,22 @@
         <v>46040</v>
       </c>
       <c r="B172" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>22.14699074074074</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>16.66956018518519</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>31.32233796296297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -11788,22 +11788,22 @@
         <v>46041</v>
       </c>
       <c r="B173" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>21.35995370370371</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>11.18055555555556</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>23.75289351851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -11820,13 +11820,13 @@
         <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>21.01851851851852</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>11.27604166666666</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>25.94328703703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -11843,13 +11843,13 @@
         <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>13.29282407407408</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>8.133680555555555</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>19.73668981481481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -11866,13 +11866,13 @@
         <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>14.76851851851852</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>9.592013888888888</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>39.67592592592592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -11889,13 +11889,13 @@
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>13.85995370370371</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>8.501157407407408</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>14.56597222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -11912,13 +11912,13 @@
         <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>15.43402777777778</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>12.29166666666667</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>38.94965277777777</v>
+        <v>0.1041666666666667</v>
       </c>
     </row>
     <row r="179">
@@ -11935,13 +11935,13 @@
         <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>14.67013888888889</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>9.377893518518519</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>34.52835648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -11955,16 +11955,16 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.04340277777777778</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>11.96180555555556</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>8.862847222222221</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>17.34375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -11978,16 +11978,16 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>9.525462962962962</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>3.816550925925926</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>15.52083333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -11995,22 +11995,22 @@
         <v>46050</v>
       </c>
       <c r="B182" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.04340277777777778</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>13.42013888888889</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>9.074074074074074</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>14.94502314814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -12024,16 +12024,16 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>12.91087962962963</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>10.16782407407407</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>15.67997685185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -12050,13 +12050,13 @@
         <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>13.00925925925926</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>10.1244212962963</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>15.18229166666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -12070,16 +12070,16 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.02604166666666667</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>16.9386574074074</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>8.217592592592592</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>21.09375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -12087,22 +12087,22 @@
         <v>46054</v>
       </c>
       <c r="B186" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>15.19675925925926</v>
+        <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>10.78125</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>24.27372685185185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -12110,22 +12110,22 @@
         <v>46055</v>
       </c>
       <c r="B187" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>13.46064814814815</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>10.62789351851852</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>18.68923611111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -12133,22 +12133,22 @@
         <v>46056</v>
       </c>
       <c r="B188" t="n">
-        <v>0.005787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.03761574074074074</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>21.50462962962963</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>11.77951388888889</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>46.22106481481481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -12156,22 +12156,22 @@
         <v>46057</v>
       </c>
       <c r="B189" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>21.90393518518518</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>17.28009259259259</v>
+        <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>49.97395833333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -12179,22 +12179,22 @@
         <v>46058</v>
       </c>
       <c r="B190" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>17.95717592592592</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>13.40567129629629</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>44.47048611111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -12202,22 +12202,22 @@
         <v>46059</v>
       </c>
       <c r="B191" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>0.09548611111111112</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>13.29861111111111</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>9.308449074074073</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>30.85648148148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -12231,16 +12231,16 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>17.65625</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>13.62268518518519</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>21.6724537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -12257,13 +12257,13 @@
         <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>18.47222222222222</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>15.72048611111111</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>46.953125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -12271,22 +12271,22 @@
         <v>46062</v>
       </c>
       <c r="B194" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>0.2604166666666667</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>17.49421296296296</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>16.06192129629629</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>43.15393518518518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -12303,13 +12303,13 @@
         <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>18.16550925925926</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>15.59895833333334</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>43.11921296296296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -12317,22 +12317,22 @@
         <v>46064</v>
       </c>
       <c r="B196" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>17.93981481481482</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>14.4212962962963</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>43.88888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -12340,22 +12340,22 @@
         <v>46065</v>
       </c>
       <c r="B197" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>17.5462962962963</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>12.82986111111111</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>49.49363425925927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -12372,13 +12372,13 @@
         <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>24.30555555555555</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>19.99421296296296</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>43.65162037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -12392,16 +12392,16 @@
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>0.06076388888888889</v>
+        <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>35.29513888888889</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>23.50694444444445</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>42.14409722222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -12415,16 +12415,16 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0.04340277777777778</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>22.3900462962963</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>15.86805555555556</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>48.29571759259259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -12432,22 +12432,22 @@
         <v>46069</v>
       </c>
       <c r="B201" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>26.85763888888889</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>21.53356481481482</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>37.61574074074074</v>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="202">
@@ -12455,22 +12455,22 @@
         <v>46070</v>
       </c>
       <c r="B202" t="n">
-        <v>0.06365740740740741</v>
+        <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>0.002893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.1331018518518519</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>19.46759259259259</v>
+        <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>13.98148148148148</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>55.6568287037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -12478,22 +12478,22 @@
         <v>46071</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0462962962962963</v>
+        <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>0.005787037037037038</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0.1128472222222222</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>21.0011574074074</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>16.49305555555555</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>37.5318287037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -12507,16 +12507,16 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.02604166666666667</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>24.43865740740741</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>10.55844907407408</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>53.70949074074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -12524,22 +12524,22 @@
         <v>46073</v>
       </c>
       <c r="B205" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>25.60185185185185</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>15.75520833333333</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>44.78877314814814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -12547,22 +12547,22 @@
         <v>46074</v>
       </c>
       <c r="B206" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>26.82870370370371</v>
+        <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>19.00462962962963</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>49.40104166666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -12579,13 +12579,13 @@
         <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>19.65856481481481</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>18.88020833333333</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>46.50462962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -12593,22 +12593,22 @@
         <v>46076</v>
       </c>
       <c r="B208" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>26.52199074074074</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>16.73900462962963</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>53.17997685185185</v>
+        <v>0.2170138888888889</v>
       </c>
     </row>
     <row r="209">
@@ -12622,16 +12622,16 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>25.54398148148148</v>
+        <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>13.0150462962963</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>52.83854166666667</v>
+        <v>0.04340277777777778</v>
       </c>
     </row>
     <row r="210">
@@ -12645,16 +12645,16 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>0.234375</v>
+        <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>23.42013888888889</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>17.06886574074074</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>41.85474537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -12668,16 +12668,16 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>19.54282407407408</v>
+        <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>13.46643518518519</v>
+        <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>37.27719907407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -12691,16 +12691,16 @@
         <v>0</v>
       </c>
       <c r="D212" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>24.34027777777778</v>
+        <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>15.50347222222222</v>
+        <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>48.94965277777777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -12714,16 +12714,16 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="E213" t="n">
-        <v>20.10995370370371</v>
+        <v>0</v>
       </c>
       <c r="F213" t="n">
-        <v>11.44097222222222</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>46.79976851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -12737,16 +12737,16 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E214" t="n">
-        <v>24.19560185185185</v>
+        <v>0</v>
       </c>
       <c r="F214" t="n">
-        <v>21.875</v>
+        <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>45.60474537037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -12754,22 +12754,22 @@
         <v>46083</v>
       </c>
       <c r="B215" t="n">
-        <v>0.0462962962962963</v>
+        <v>0</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>0.1273148148148148</v>
+        <v>0</v>
       </c>
       <c r="E215" t="n">
-        <v>15.17939814814815</v>
+        <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>12.14699074074074</v>
+        <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>43.61979166666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -12783,16 +12783,16 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>15.23726851851852</v>
+        <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>13.9380787037037</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>42.71701388888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -12806,16 +12806,16 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>22.06018518518519</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>16.90972222222222</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>44.13773148148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -12832,13 +12832,13 @@
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>19.11458333333333</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>12.03125</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>42.54340277777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -12852,16 +12852,16 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>26.79976851851852</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>17.9369212962963</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>45.50636574074074</v>
+        <v>0.008680555555555556</v>
       </c>
     </row>
     <row r="220">
@@ -12869,22 +12869,22 @@
         <v>46088</v>
       </c>
       <c r="B220" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>19.14351851851852</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>15.00868055555556</v>
+        <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>39.9537037037037</v>
+        <v>0.04340277777777778</v>
       </c>
     </row>
     <row r="221">
@@ -12892,22 +12892,22 @@
         <v>46089</v>
       </c>
       <c r="B221" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.06655092592592593</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>20.96643518518518</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>16.0300925925926</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>42.578125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -12921,16 +12921,16 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.078125</v>
+        <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>17.62731481481481</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>12.85590277777778</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>41.10532407407408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -12938,22 +12938,22 @@
         <v>46091</v>
       </c>
       <c r="B223" t="n">
-        <v>0.1678240740740741</v>
+        <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0.2748842592592593</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>20.86805555555556</v>
+        <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>14.42708333333333</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>42.44791666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -12961,22 +12961,22 @@
         <v>46092</v>
       </c>
       <c r="B224" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.2170138888888889</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>19.17824074074074</v>
+        <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>12.33217592592592</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>37.76909722222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -12984,22 +12984,22 @@
         <v>46093</v>
       </c>
       <c r="B225" t="n">
-        <v>0.1331018518518519</v>
+        <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>0.03182870370370371</v>
+        <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.2256944444444444</v>
+        <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>18.29861111111111</v>
+        <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>9.49363425925926</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>47.75462962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -13007,22 +13007,22 @@
         <v>46094</v>
       </c>
       <c r="B226" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>0.07233796296296297</v>
+        <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.2141203703703704</v>
+        <v>0</v>
       </c>
       <c r="E226" t="n">
-        <v>24.4212962962963</v>
+        <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>11.87789351851852</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>49.04803240740741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -13030,22 +13030,22 @@
         <v>46095</v>
       </c>
       <c r="B227" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>0.02025462962962963</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.162037037037037</v>
+        <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>21.41782407407408</v>
+        <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>11.22685185185185</v>
+        <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>51.91261574074073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -13053,22 +13053,22 @@
         <v>46096</v>
       </c>
       <c r="B228" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>28.75578703703704</v>
+        <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>16.78819444444444</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>53.51851851851852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -13076,22 +13076,22 @@
         <v>46097</v>
       </c>
       <c r="B229" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0.373263888888889</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>26.34837962962963</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>15.34432870370371</v>
+        <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>55.64236111111111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -13099,22 +13099,22 @@
         <v>46098</v>
       </c>
       <c r="B230" t="n">
-        <v>0.04050925925925926</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>0.002893518518518519</v>
+        <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.1215277777777778</v>
+        <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>18.00347222222222</v>
+        <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>10.11284722222222</v>
+        <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>58.48958333333334</v>
+        <v>0.05208333333333334</v>
       </c>
     </row>
     <row r="231">
@@ -13122,22 +13122,22 @@
         <v>46099</v>
       </c>
       <c r="B231" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.2777777777777778</v>
+        <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>21.15162037037037</v>
+        <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>10.63368055555556</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>55.79282407407408</v>
+        <v>0.05208333333333334</v>
       </c>
     </row>
     <row r="232">
@@ -13145,22 +13145,22 @@
         <v>46100</v>
       </c>
       <c r="B232" t="n">
-        <v>0.09837962962962962</v>
+        <v>0</v>
       </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.2054398148148148</v>
+        <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>23.14814814814815</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>13.37962962962963</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>53.17708333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -13168,22 +13168,22 @@
         <v>46101</v>
       </c>
       <c r="B233" t="n">
-        <v>0.1099537037037037</v>
+        <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.1591435185185185</v>
+        <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>19.06828703703704</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>7.803819444444445</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>56.42650462962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -13191,22 +13191,22 @@
         <v>46102</v>
       </c>
       <c r="B234" t="n">
-        <v>2.494212962962963</v>
+        <v>2.152777777777777</v>
       </c>
       <c r="C234" t="n">
-        <v>0.1186342592592593</v>
+        <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>4.913194444444445</v>
+        <v>4.305555555555554</v>
       </c>
       <c r="E234" t="n">
-        <v>22.63888888888889</v>
+        <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>9.655671296296296</v>
+        <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>53.75578703703704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -13214,22 +13214,22 @@
         <v>46103</v>
       </c>
       <c r="B235" t="n">
-        <v>33.57638888888889</v>
+        <v>31.5625</v>
       </c>
       <c r="C235" t="n">
-        <v>4.904513888888889</v>
+        <v>3.055555555555555</v>
       </c>
       <c r="D235" t="n">
-        <v>62.15277777777778</v>
+        <v>60.06944444444444</v>
       </c>
       <c r="E235" t="n">
-        <v>25.30092592592593</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>9.72800925925926</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>48.18287037037037</v>
+        <v>0.15625</v>
       </c>
     </row>
     <row r="236">
@@ -13237,22 +13237,22 @@
         <v>46104</v>
       </c>
       <c r="B236" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.3993055555555556</v>
+        <v>0</v>
       </c>
       <c r="E236" t="n">
-        <v>24.12037037037037</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>11.40046296296296</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>40.73784722222223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -13260,22 +13260,22 @@
         <v>46105</v>
       </c>
       <c r="B237" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E237" t="n">
-        <v>20.32986111111111</v>
+        <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>8.376736111111111</v>
+        <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>31.82291666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -13283,22 +13283,22 @@
         <v>46106</v>
       </c>
       <c r="B238" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C238" t="n">
         <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>10.74074074074074</v>
+        <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>7.158564814814814</v>
+        <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>21.05902777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -13306,22 +13306,22 @@
         <v>46107</v>
       </c>
       <c r="B239" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>0.2170138888888889</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>22.15856481481482</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>12.00520833333333</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>39.62962962962963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -13329,22 +13329,22 @@
         <v>46108</v>
       </c>
       <c r="B240" t="n">
-        <v>0.02893518518518519</v>
+        <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="D240" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>16.28472222222222</v>
+        <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>5.830439814814815</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>45.18518518518518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -13352,22 +13352,22 @@
         <v>46109</v>
       </c>
       <c r="B241" t="n">
-        <v>0.05787037037037037</v>
+        <v>0</v>
       </c>
       <c r="C241" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="D241" t="n">
-        <v>0.1244212962962963</v>
+        <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>24.23032407407408</v>
+        <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>16.55381944444444</v>
+        <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>45.15335648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -13375,22 +13375,22 @@
         <v>46110</v>
       </c>
       <c r="B242" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C242" t="n">
         <v>0</v>
       </c>
       <c r="D242" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E242" t="n">
-        <v>23.98148148148148</v>
+        <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>13.6255787037037</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>52.2193287037037</v>
+        <v>0.05208333333333334</v>
       </c>
     </row>
     <row r="243">
@@ -13398,22 +13398,22 @@
         <v>46111</v>
       </c>
       <c r="B243" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C243" t="n">
         <v>0</v>
       </c>
       <c r="D243" t="n">
-        <v>0.1736111111111111</v>
+        <v>0</v>
       </c>
       <c r="E243" t="n">
-        <v>22.3900462962963</v>
+        <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>8.914930555555555</v>
+        <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>50.30960648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -13421,22 +13421,22 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C244" t="n">
         <v>0</v>
       </c>
       <c r="D244" t="n">
-        <v>0.2170138888888889</v>
+        <v>0</v>
       </c>
       <c r="E244" t="n">
-        <v>20.5324074074074</v>
+        <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>18.203125</v>
+        <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>38.14814814814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -13444,22 +13444,22 @@
         <v>46113</v>
       </c>
       <c r="B245" t="n">
-        <v>0.08680555555555555</v>
+        <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
-        <v>0.1475694444444445</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
-        <v>12.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>5.109953703703703</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>31.78240740740741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -13467,22 +13467,22 @@
         <v>46114</v>
       </c>
       <c r="B246" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>0.04340277777777778</v>
+        <v>0</v>
       </c>
       <c r="D246" t="n">
-        <v>0.1649305555555556</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>11.81134259259259</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>3.625578703703704</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>20.15335648148148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -13496,16 +13496,16 @@
         <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E247" t="n">
-        <v>22.96296296296296</v>
+        <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>8.096064814814815</v>
+        <v>0</v>
       </c>
       <c r="G247" t="n">
-        <v>37.84722222222221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -13513,22 +13513,22 @@
         <v>46116</v>
       </c>
       <c r="B248" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
         <v>0</v>
       </c>
       <c r="D248" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>14.12615740740741</v>
+        <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>7.456597222222222</v>
+        <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>23.03530092592593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -13545,13 +13545,13 @@
         <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>27.30902777777778</v>
+        <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>26.11400462962963</v>
+        <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>27.78356481481482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -13565,16 +13565,16 @@
         <v>0</v>
       </c>
       <c r="D250" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E250" t="n">
-        <v>17.04861111111111</v>
+        <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>16.38599537037037</v>
+        <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>22.58969907407407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -13582,22 +13582,22 @@
         <v>46119</v>
       </c>
       <c r="B251" t="n">
-        <v>0.1041666666666667</v>
+        <v>0</v>
       </c>
       <c r="C251" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="D251" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="E251" t="n">
-        <v>12.66782407407407</v>
+        <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>10.83043981481482</v>
+        <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>17.78645833333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -13611,16 +13611,16 @@
         <v>0</v>
       </c>
       <c r="D252" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>7.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>2.065972222222222</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>21.00694444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -13628,22 +13628,22 @@
         <v>46121</v>
       </c>
       <c r="B253" t="n">
-        <v>0.08101851851851852</v>
+        <v>0</v>
       </c>
       <c r="C253" t="n">
         <v>0</v>
       </c>
       <c r="D253" t="n">
-        <v>0.1793981481481482</v>
+        <v>0</v>
       </c>
       <c r="E253" t="n">
-        <v>6.40625</v>
+        <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>1.81712962962963</v>
+        <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>19.03356481481482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -13651,22 +13651,22 @@
         <v>46122</v>
       </c>
       <c r="B254" t="n">
-        <v>0.04050925925925926</v>
+        <v>0</v>
       </c>
       <c r="C254" t="n">
         <v>0</v>
       </c>
       <c r="D254" t="n">
-        <v>0.1244212962962963</v>
+        <v>0</v>
       </c>
       <c r="E254" t="n">
-        <v>12.33796296296296</v>
+        <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>7.800925925925926</v>
+        <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>19.69618055555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -13674,22 +13674,22 @@
         <v>46123</v>
       </c>
       <c r="B255" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C255" t="n">
         <v>0</v>
       </c>
       <c r="D255" t="n">
-        <v>0.3211805555555556</v>
+        <v>0</v>
       </c>
       <c r="E255" t="n">
-        <v>17.84722222222222</v>
+        <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>11.67534722222222</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>25.97222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -13697,22 +13697,22 @@
         <v>46124</v>
       </c>
       <c r="B256" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="D256" t="n">
-        <v>0.15625</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
-        <v>15.79861111111111</v>
+        <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>11.92997685185185</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>16.2037037037037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -13720,22 +13720,22 @@
         <v>46125</v>
       </c>
       <c r="B257" t="n">
-        <v>0.1273148148148148</v>
+        <v>17.5</v>
       </c>
       <c r="C257" t="n">
-        <v>0.05208333333333334</v>
+        <v>17.5</v>
       </c>
       <c r="D257" t="n">
-        <v>0.2719907407407408</v>
+        <v>17.5</v>
       </c>
       <c r="E257" t="n">
-        <v>9.768518518518517</v>
+        <v>17.5</v>
       </c>
       <c r="F257" t="n">
-        <v>7.586805555555555</v>
+        <v>17.5</v>
       </c>
       <c r="G257" t="n">
-        <v>15.11863425925926</v>
+        <v>17.5</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_Fig05_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D2 Temporal Continuity & Information Availability/artifacts/data/D2_Fig05_source_data.xlsx
@@ -552,11 +552,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>info_empty_cov</t>
+          <t>hard_stasis_fraction_observed</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3847410553831073</v>
+        <v>0.01198452906248298</v>
       </c>
     </row>
     <row r="9">
@@ -567,11 +567,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>info_empty_cov</t>
+          <t>hard_stasis_fraction_observed</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6246256058378261</v>
+        <v>0.2543988669172523</v>
       </c>
     </row>
   </sheetData>
@@ -5125,7 +5125,7 @@
         <v>45882</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -5136,10 +5136,10 @@
         <v>45883</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4166666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5147,10 +5147,10 @@
         <v>45884</v>
       </c>
       <c r="B16" t="n">
-        <v>9.027777777777777</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.611111111111112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5367,10 +5367,10 @@
         <v>45904</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5455,10 +5455,10 @@
         <v>45912</v>
       </c>
       <c r="B44" t="n">
-        <v>25.20833333333333</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>25.34722222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5788,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -5807,7 +5807,7 @@
         <v>45944</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
@@ -5818,10 +5818,10 @@
         <v>45945</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5840,10 +5840,10 @@
         <v>45947</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5851,7 +5851,7 @@
         <v>45948</v>
       </c>
       <c r="B80" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -5873,10 +5873,10 @@
         <v>45950</v>
       </c>
       <c r="B82" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5884,7 +5884,7 @@
         <v>45951</v>
       </c>
       <c r="B83" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5906,7 +5906,7 @@
         <v>45953</v>
       </c>
       <c r="B85" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -5920,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5939,10 +5939,10 @@
         <v>45956</v>
       </c>
       <c r="B88" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5950,7 +5950,7 @@
         <v>45957</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="C90" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5972,10 +5972,10 @@
         <v>45959</v>
       </c>
       <c r="B91" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1157407407407408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -6005,10 +6005,10 @@
         <v>45962</v>
       </c>
       <c r="B94" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6203,10 +6203,10 @@
         <v>45980</v>
       </c>
       <c r="B112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6214,10 +6214,10 @@
         <v>45981</v>
       </c>
       <c r="B113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6731,10 +6731,10 @@
         <v>46028</v>
       </c>
       <c r="B160" t="n">
-        <v>36.21527777777778</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -6742,10 +6742,10 @@
         <v>46029</v>
       </c>
       <c r="B161" t="n">
-        <v>3.993055555555555</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -7798,10 +7798,10 @@
         <v>46125</v>
       </c>
       <c r="B257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8154,22 +8154,22 @@
         <v>45883</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3472222222222222</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3472222222222222</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3993055555555556</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3472222222222222</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3472222222222222</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3645833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8177,22 +8177,22 @@
         <v>45884</v>
       </c>
       <c r="B16" t="n">
-        <v>8.888888888888889</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>8.680555555555557</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.097222222222221</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>8.912037037037038</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>8.767361111111111</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9.02199074074074</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -8637,22 +8637,22 @@
         <v>45904</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2083333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -8821,22 +8821,22 @@
         <v>45912</v>
       </c>
       <c r="B44" t="n">
-        <v>25.3125</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>25.20833333333333</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>25.41666666666667</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>25.27777777777778</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>25.20833333333333</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>25.39930555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -9540,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.02604166666666667</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -9557,13 +9557,13 @@
         <v>45944</v>
       </c>
       <c r="B76" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -9586,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.06944444444444445</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -9609,7 +9609,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.03472222222222222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -9649,13 +9649,13 @@
         <v>45948</v>
       </c>
       <c r="B80" t="n">
-        <v>0.01736111111111111</v>
+        <v>0</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0607638888888889</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -9701,7 +9701,7 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.008680555555555556</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -9764,13 +9764,13 @@
         <v>45953</v>
       </c>
       <c r="B85" t="n">
-        <v>0.01157407407407408</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.05787037037037038</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -9787,13 +9787,13 @@
         <v>45954</v>
       </c>
       <c r="B86" t="n">
-        <v>0.02314814814814815</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.06365740740740741</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -9871,7 +9871,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.05208333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -10385,22 +10385,22 @@
         <v>45980</v>
       </c>
       <c r="B112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>1.180555555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -10408,22 +10408,22 @@
         <v>45981</v>
       </c>
       <c r="B113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.1388888888888889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -11489,22 +11489,22 @@
         <v>46028</v>
       </c>
       <c r="B160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>36.18055555555556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -11512,22 +11512,22 @@
         <v>46029</v>
       </c>
       <c r="B161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>3.958333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -13720,22 +13720,22 @@
         <v>46125</v>
       </c>
       <c r="B257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="D257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="E257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="G257" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
